--- a/Result/profitability/3002.xlsx
+++ b/Result/profitability/3002.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06875000000000001</v>
+        <v>0.07375000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>19.06375</v>
+        <v>17.8</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.11125</v>
+        <v>0.12125</v>
       </c>
       <c r="N3" t="n">
-        <v>21.42375</v>
+        <v>19.8525</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1675</v>
+        <v>0.1725</v>
       </c>
       <c r="N4" t="n">
-        <v>23.49375</v>
+        <v>22.08625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2175</v>
+        <v>0.18875</v>
       </c>
       <c r="N5" t="n">
-        <v>26.35</v>
+        <v>25.4525</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>0.20875</v>
+        <v>0.1925</v>
       </c>
       <c r="N6" t="n">
-        <v>29.1125</v>
+        <v>27.74875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.33875</v>
+        <v>0.36</v>
       </c>
       <c r="N7" t="n">
-        <v>32.55875</v>
+        <v>31.545</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0.435</v>
+        <v>0.4425</v>
       </c>
       <c r="N8" t="n">
-        <v>35.825</v>
+        <v>35.885</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>223</v>
+      </c>
+      <c r="D75" t="n">
+        <v>203</v>
+      </c>
+      <c r="E75" t="n">
+        <v>20</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04625000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.3775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4800000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05687203791469209</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8214285714285714</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.180000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4459627329192547</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
